--- a/hira_material_automation/output/monthly/202601_202607__epidural_adhesion_barrier__900129__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202607__epidural_adhesion_barrier__900129__normalized.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-04T22:32:47</t>
+          <t>2026-07-14T22:32:38</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>45aa48080695208e249854e5f17545bfd70c47fa803fe42bcaf566be187788f3</t>
+          <t>88d3de0e5cb8a6a969538954295865431d595ae5baf96ff2ff398c874cd08f47</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202607__epidural_adhesion_barrier__900129__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202607__epidural_adhesion_barrier__900129__normalized.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-14T22:32:38</t>
+          <t>2026-07-24T22:39:33</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>88d3de0e5cb8a6a969538954295865431d595ae5baf96ff2ff398c874cd08f47</t>
+          <t>40ad9db351b83a725eee102bdad48fb68e60697565402ccf8f2a9f7207a507ad</t>
         </is>
       </c>
     </row>
